--- a/artfynd/A 172-2024 artfynd.xlsx
+++ b/artfynd/A 172-2024 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
